--- a/01_Thermal/B_results/single_var_params.xlsx
+++ b/01_Thermal/B_results/single_var_params.xlsx
@@ -455,13 +455,13 @@
         <v>0.2</v>
       </c>
       <c r="B2" t="n">
-        <v>9.81871600999718</v>
+        <v>9.374180388204705</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3606708149646707</v>
+        <v>0.3776315323535362</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1081376915556098</v>
+        <v>0.03497836639026616</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>6.770606011794623</v>
+        <v>6.673280221219098</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4887648872788611</v>
+        <v>0.4967946167382579</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002531838719378788</v>
+        <v>0.001727985030488323</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>5.545970949951865</v>
+        <v>3.291672626834772</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6090783651875445</v>
+        <v>0.7031244562920843</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001164258275031974</v>
+        <v>-0.00182925596811175</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>3.970100616203556</v>
+        <v>3.914862849292072</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6298678560555186</v>
+        <v>0.6433688944307844</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01142640831556188</v>
+        <v>0.009147623214956957</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>1.1</v>
       </c>
       <c r="B6" t="n">
-        <v>2.957780394786506</v>
+        <v>3.029721252549283</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6999404560883336</v>
+        <v>0.7027402961340202</v>
       </c>
       <c r="D6" t="n">
-        <v>9.537204570494757e-06</v>
+        <v>-0.0009037041805251279</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>1.6</v>
       </c>
       <c r="B7" t="n">
-        <v>3.185712397796389</v>
+        <v>3.110588816707562</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6999562287719225</v>
+        <v>0.744074370343986</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.02006838017244906</v>
+        <v>-0.01137067090462262</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>2.2</v>
       </c>
       <c r="B8" t="n">
-        <v>2.582349146612595</v>
+        <v>2.4535639299596</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7728403324973639</v>
+        <v>0.8300884365084038</v>
       </c>
       <c r="D8" t="n">
-        <v>8.906684255805699e-05</v>
+        <v>-0.006633976675569533</v>
       </c>
     </row>
   </sheetData>
